--- a/data/matieres.xlsx
+++ b/data/matieres.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\pilotage-stock-production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077F80F6-066D-4724-9784-A780193C2586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA80C39-D5FD-45BE-B619-DA0270B28D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="matieres" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/data/matieres.xlsx
+++ b/data/matieres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\pilotage-stock-production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59990CEA-30F6-4207-8568-F0E5FF3EC44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A092A6A-6E63-4630-BBD0-3BE63EC5E841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="204">
   <si>
     <t>code_matiere</t>
   </si>
@@ -1254,7 +1254,9 @@
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D7" s="3">
         <v>1</v>
       </c>
@@ -1280,7 +1282,9 @@
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D8" s="3">
         <v>4</v>
       </c>
@@ -1306,7 +1310,9 @@
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D9" s="3">
         <v>5</v>
       </c>
@@ -1332,7 +1338,9 @@
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D10" s="3">
         <v>4</v>
       </c>
@@ -1358,7 +1366,9 @@
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
@@ -1474,7 +1484,9 @@
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D15" s="3">
         <v>3</v>
       </c>
@@ -1500,7 +1512,9 @@
       <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D16" s="3">
         <v>1</v>
       </c>
@@ -1526,7 +1540,9 @@
       <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
@@ -1552,7 +1568,9 @@
       <c r="B18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D18" s="3">
         <v>3</v>
       </c>
@@ -1578,7 +1596,9 @@
       <c r="B19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D19" s="3">
         <v>3</v>
       </c>
@@ -1604,7 +1624,9 @@
       <c r="B20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D20" s="3">
         <v>4</v>
       </c>
@@ -1630,7 +1652,9 @@
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D21" s="3">
         <v>3</v>
       </c>
@@ -1656,7 +1680,9 @@
       <c r="B22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D22" s="3">
         <v>3</v>
       </c>
@@ -1682,7 +1708,9 @@
       <c r="B23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D23" s="3">
         <v>3</v>
       </c>
@@ -1708,7 +1736,9 @@
       <c r="B24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D24" s="3">
         <v>3</v>
       </c>
@@ -1734,7 +1764,9 @@
       <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D25" s="3">
         <v>4</v>
       </c>
@@ -1850,7 +1882,9 @@
       <c r="B29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D29" s="3">
         <v>208</v>
       </c>
@@ -1906,7 +1940,9 @@
       <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D31" s="3">
         <v>85</v>
       </c>
@@ -2050,7 +2086,9 @@
       <c r="B36" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D36" s="3">
         <v>0</v>
       </c>
@@ -3272,7 +3310,9 @@
       <c r="B77" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C77" s="2"/>
+      <c r="C77" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="D77" s="3">
         <v>0</v>
       </c>

--- a/data/matieres.xlsx
+++ b/data/matieres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\pilotage-stock-production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A092A6A-6E63-4630-BBD0-3BE63EC5E841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2D010C-F8DA-4B1B-9063-F73D6369A058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -688,7 +688,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,6 +719,12 @@
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -732,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -750,6 +756,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1260,7 +1267,9 @@
       <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="15">
+        <v>5</v>
+      </c>
       <c r="F7" s="5">
         <v>1742.8420000000001</v>
       </c>
@@ -1288,7 +1297,9 @@
       <c r="D8" s="3">
         <v>4</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="15">
+        <v>5</v>
+      </c>
       <c r="F8" s="5">
         <v>1588.768</v>
       </c>
@@ -1316,7 +1327,9 @@
       <c r="D9" s="3">
         <v>5</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="15">
+        <v>5</v>
+      </c>
       <c r="F9" s="5">
         <v>2903.5</v>
       </c>
@@ -1344,7 +1357,9 @@
       <c r="D10" s="3">
         <v>4</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="15">
+        <v>5</v>
+      </c>
       <c r="F10" s="5">
         <v>2536.366</v>
       </c>
@@ -1372,7 +1387,9 @@
       <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="15">
+        <v>5</v>
+      </c>
       <c r="F11" s="5">
         <v>3893.6909999999998</v>
       </c>
@@ -1490,7 +1507,9 @@
       <c r="D15" s="3">
         <v>3</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="15">
+        <v>5</v>
+      </c>
       <c r="F15" s="5">
         <v>1907.414</v>
       </c>
@@ -1518,7 +1537,9 @@
       <c r="D16" s="3">
         <v>1</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="15">
+        <v>5</v>
+      </c>
       <c r="F16" s="5">
         <v>1490.4369999999999</v>
       </c>
@@ -1546,7 +1567,9 @@
       <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="15">
+        <v>5</v>
+      </c>
       <c r="F17" s="5">
         <v>2741.3690000000001</v>
       </c>
@@ -1574,7 +1597,9 @@
       <c r="D18" s="3">
         <v>3</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="15">
+        <v>5</v>
+      </c>
       <c r="F18" s="5">
         <v>1468.8230000000001</v>
       </c>
@@ -1602,7 +1627,9 @@
       <c r="D19" s="3">
         <v>3</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="15">
+        <v>5</v>
+      </c>
       <c r="F19" s="5">
         <v>1898.335</v>
       </c>
@@ -1630,7 +1657,9 @@
       <c r="D20" s="3">
         <v>4</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="15">
+        <v>5</v>
+      </c>
       <c r="F20" s="5">
         <v>2208.9740000000002</v>
       </c>
@@ -1658,7 +1687,9 @@
       <c r="D21" s="3">
         <v>3</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="15">
+        <v>5</v>
+      </c>
       <c r="F21" s="5">
         <v>1907.414</v>
       </c>
@@ -1686,7 +1717,9 @@
       <c r="D22" s="3">
         <v>3</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="15">
+        <v>5</v>
+      </c>
       <c r="F22" s="5">
         <v>1907.414</v>
       </c>
@@ -1714,7 +1747,9 @@
       <c r="D23" s="3">
         <v>3</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="15">
+        <v>5</v>
+      </c>
       <c r="F23" s="5">
         <v>1468.8230000000001</v>
       </c>
@@ -1742,7 +1777,9 @@
       <c r="D24" s="3">
         <v>3</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="15">
+        <v>5</v>
+      </c>
       <c r="F24" s="5">
         <v>1898.335</v>
       </c>
@@ -1770,7 +1807,9 @@
       <c r="D25" s="3">
         <v>4</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="15">
+        <v>5</v>
+      </c>
       <c r="F25" s="5">
         <v>2208.9740000000002</v>
       </c>
@@ -1888,7 +1927,9 @@
       <c r="D29" s="3">
         <v>208</v>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="15">
+        <v>105</v>
+      </c>
       <c r="F29" s="5">
         <v>6.4279999999999999</v>
       </c>
@@ -1946,7 +1987,9 @@
       <c r="D31" s="3">
         <v>85</v>
       </c>
-      <c r="E31" s="4"/>
+      <c r="E31" s="15">
+        <v>20</v>
+      </c>
       <c r="F31" s="5">
         <v>0.1</v>
       </c>
@@ -2092,7 +2135,9 @@
       <c r="D36" s="3">
         <v>0</v>
       </c>
-      <c r="E36" s="4"/>
+      <c r="E36" s="15">
+        <v>20</v>
+      </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5">
         <v>0</v>
@@ -3316,7 +3361,9 @@
       <c r="D77" s="3">
         <v>0</v>
       </c>
-      <c r="E77" s="4"/>
+      <c r="E77" s="15">
+        <v>5</v>
+      </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5">
         <v>16.914000000000001</v>
